--- a/docs/QA_TRACKER.xlsx
+++ b/docs/QA_TRACKER.xlsx
@@ -61,7 +61,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -81,11 +81,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E6F7F3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3E0"/>
       </patternFill>
     </fill>
   </fills>
@@ -115,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -136,12 +131,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -165,7 +154,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -541,7 +529,7 @@
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="46" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -2712,14 +2700,14 @@
           <t>Lands on worker home with assigned jobs</t>
         </is>
       </c>
-      <c r="G47" s="8" t="inlineStr">
-        <is>
-          <t>Automated - needs E2E_WORKER_EMAIL / E2E_WORKER_PASSWORD</t>
-        </is>
-      </c>
-      <c r="H47" s="9" t="inlineStr">
-        <is>
-          <t>Until enabled</t>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>Automated (CI) - via worker account secrets</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr"/>
@@ -2758,14 +2746,14 @@
           <t>Only this worker's assigned jobs show, correct times (AM/PM)</t>
         </is>
       </c>
-      <c r="G48" s="8" t="inlineStr">
-        <is>
-          <t>Automated - needs E2E_WORKER_EMAIL / E2E_WORKER_PASSWORD</t>
-        </is>
-      </c>
-      <c r="H48" s="9" t="inlineStr">
-        <is>
-          <t>Until enabled</t>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>Automated (CI) - via worker account secrets</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr"/>
@@ -2850,14 +2838,14 @@
           <t>Time entry recorded with correct duration</t>
         </is>
       </c>
-      <c r="G50" s="8" t="inlineStr">
-        <is>
-          <t>Automated - needs E2E_WORKER_EMAIL / E2E_WORKER_PASSWORD</t>
-        </is>
-      </c>
-      <c r="H50" s="9" t="inlineStr">
-        <is>
-          <t>Until enabled</t>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>Automated (CI) - via worker account secrets</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr"/>
@@ -4184,14 +4172,14 @@
           <t>No cross-company data leakage (RLS)</t>
         </is>
       </c>
-      <c r="G79" s="8" t="inlineStr">
-        <is>
-          <t>Automated - needs E2E_EMAIL_2 / E2E_PASSWORD_2 (2nd company)</t>
-        </is>
-      </c>
-      <c r="H79" s="9" t="inlineStr">
-        <is>
-          <t>Until enabled</t>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>Automated (CI) - via 2nd company secrets</t>
+        </is>
+      </c>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr"/>
@@ -4449,7 +4437,7 @@
   <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -4460,252 +4448,252 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Beta readiness - QA coverage</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Coverage is derived from the Cypress specs themselves. Counts are live formulas - they update as you record results.</t>
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Coverage is derived from the Cypress specs. Counts are live formulas - they update as you record results.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Manual to run</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>Not yet run</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="11">
         <f>COUNTIF('Test Cases'!$C$2:$C$84,A6)</f>
         <v/>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="11">
         <f>COUNTIFS('Test Cases'!$C$2:$C$84,A6,'Test Cases'!$G$2:$G$84,"Automated*")</f>
         <v/>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="11">
         <f>B6-C6</f>
         <v/>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="11">
         <f>COUNTIFS('Test Cases'!$C$2:$C$84,A6,'Test Cases'!$I$2:$I$84,"Pass")</f>
         <v/>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="11">
         <f>COUNTIFS('Test Cases'!$C$2:$C$84,A6,'Test Cases'!$I$2:$I$84,"Fail")</f>
         <v/>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="11">
         <f>COUNTIFS('Test Cases'!$C$2:$C$84,A6,'Test Cases'!$I$2:$I$84,"Blocked")</f>
         <v/>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="11">
         <f>D6-E6-F6-G6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="11">
         <f>COUNTIF('Test Cases'!$C$2:$C$84,A7)</f>
         <v/>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="11">
         <f>COUNTIFS('Test Cases'!$C$2:$C$84,A7,'Test Cases'!$G$2:$G$84,"Automated*")</f>
         <v/>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="11">
         <f>B7-C7</f>
         <v/>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="11">
         <f>COUNTIFS('Test Cases'!$C$2:$C$84,A7,'Test Cases'!$I$2:$I$84,"Pass")</f>
         <v/>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="11">
         <f>COUNTIFS('Test Cases'!$C$2:$C$84,A7,'Test Cases'!$I$2:$I$84,"Fail")</f>
         <v/>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="11">
         <f>COUNTIFS('Test Cases'!$C$2:$C$84,A7,'Test Cases'!$I$2:$I$84,"Blocked")</f>
         <v/>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="11">
         <f>D7-E7-F7-G7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="11">
         <f>COUNTIF('Test Cases'!$C$2:$C$84,A8)</f>
         <v/>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="11">
         <f>COUNTIFS('Test Cases'!$C$2:$C$84,A8,'Test Cases'!$G$2:$G$84,"Automated*")</f>
         <v/>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="11">
         <f>B8-C8</f>
         <v/>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="11">
         <f>COUNTIFS('Test Cases'!$C$2:$C$84,A8,'Test Cases'!$I$2:$I$84,"Pass")</f>
         <v/>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="11">
         <f>COUNTIFS('Test Cases'!$C$2:$C$84,A8,'Test Cases'!$I$2:$I$84,"Fail")</f>
         <v/>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="11">
         <f>COUNTIFS('Test Cases'!$C$2:$C$84,A8,'Test Cases'!$I$2:$I$84,"Blocked")</f>
         <v/>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="11">
         <f>D8-E8-F8-G8</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="12">
         <f>SUM(B6:B8)</f>
         <v/>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="12">
         <f>SUM(C6:C8)</f>
         <v/>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="12">
         <f>SUM(D6:D8)</f>
         <v/>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="12">
         <f>SUM(E6:E8)</f>
         <v/>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="12">
         <f>SUM(F6:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="12">
         <f>SUM(G6:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="14">
+      <c r="H9" s="12">
         <f>SUM(H6:H8)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Beta gate (P0)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>P0 still to run manually</t>
         </is>
       </c>
-      <c r="B12" s="14">
+      <c r="B12" s="12">
         <f>H6</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>P0 failures outstanding</t>
         </is>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="12">
         <f>F6</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>Ready to invite testers?</t>
         </is>
       </c>
-      <c r="B14" s="17">
+      <c r="B14" s="15">
         <f>IF(AND(B12=0,B13=0),"YES - P0 clear","NOT YET")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>All automated specs are confirmed executing (not skipping) - verified green on sandbox 2026-08-21 (run 32455675720).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>For the routine pre-release pass use docs/PRE_RELEASE_CHECKLIST.md (~10 min).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>This workbook is for the one-time full sweep before beta.</t>
         </is>
       </c>
     </row>
@@ -4720,219 +4708,243 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="92" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>How to use this tracker</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="inlineStr"/>
-      <c r="B3" s="18" t="inlineStr"/>
+      <c r="A3" s="14" t="inlineStr"/>
+      <c r="B3" s="16" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>You fill in (yellow cells only):</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr"/>
+      <c r="B4" s="16" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>Pick Pass / Fail / Blocked / Skipped from the dropdown.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>When you ran it.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Tester</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Who ran it.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Notes / Bug #</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>What broke, or a link to the bug.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr"/>
-      <c r="B9" s="18" t="inlineStr"/>
+      <c r="A9" s="14" t="inlineStr"/>
+      <c r="B9" s="16" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>Colour key:</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr"/>
+      <c r="B10" s="16" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>Teal</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>Automated - already runs in CI on every push. Do NOT re-click by hand.</t>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Automated - runs in CI on every push. Do NOT re-click these by hand.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>Amber</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>Automated but not yet enabled - add the named secrets. Run manually until then.</t>
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>A cell for you to fill in.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A cell for you to fill in.</t>
-        </is>
-      </c>
+      <c r="A13" s="14" t="inlineStr"/>
+      <c r="B13" s="16" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr"/>
-      <c r="B14" s="18" t="inlineStr"/>
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>On the credential-dependent specs:</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>TC-X-01</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Multi-tenant isolation. Needs E2E_EMAIL_2 / E2E_PASSWORD_2 - configured, and verified green on sandbox 2026-08-21 (run 32455675720).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>TC-WORK-01/02/04</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Worker app. Needs E2E_WORKER_EMAIL / E2E_WORKER_PASSWORD - configured, and verified green on sandbox 2026-08-21 (run 32455675720).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr"/>
+      <c r="B17" s="16" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>Where to test:</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>Sandbox</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>https://sandbox--lively-yeot-c640cd.netlify.app - run the whole matrix here, never production.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="16" t="inlineStr"/>
-      <c r="B17" s="18" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="19" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr"/>
+      <c r="B20" s="16" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>Stripe test cards:</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>Success</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>4242 4242 4242 4242</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>Decline</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>4000 0000 0000 0002</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>3D Secure</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>4000 0025 0000 3155</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr"/>
-      <c r="B22" s="18" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="19" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr"/>
+      <c r="B25" s="16" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>Example row (format only - not a real result):</t>
         </is>
       </c>
-      <c r="B23" s="18" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>TC-AUTH-01</t>
         </is>
       </c>
-      <c r="B24" s="18" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>Pass  |  2026-08-21  |  MV  |  Confirmation email arrived in ~30s</t>
         </is>
